--- a/artfynd/A 47662-2025 artfynd.xlsx
+++ b/artfynd/A 47662-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122118605</v>
       </c>
       <c r="B2" t="n">
-        <v>110729</v>
+        <v>110732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47662-2025 artfynd.xlsx
+++ b/artfynd/A 47662-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122118605</v>
       </c>
       <c r="B2" t="n">
-        <v>110732</v>
+        <v>110819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47662-2025 artfynd.xlsx
+++ b/artfynd/A 47662-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122118605</v>
       </c>
       <c r="B2" t="n">
-        <v>110819</v>
+        <v>110822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47662-2025 artfynd.xlsx
+++ b/artfynd/A 47662-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122118605</v>
       </c>
       <c r="B2" t="n">
-        <v>110822</v>
+        <v>110848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47662-2025 artfynd.xlsx
+++ b/artfynd/A 47662-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122118605</v>
       </c>
       <c r="B2" t="n">
-        <v>110848</v>
+        <v>110849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47662-2025 artfynd.xlsx
+++ b/artfynd/A 47662-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122118605</v>
       </c>
       <c r="B2" t="n">
-        <v>110849</v>
+        <v>110850</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47662-2025 artfynd.xlsx
+++ b/artfynd/A 47662-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122118605</v>
+        <v>58716499</v>
       </c>
       <c r="B2" t="n">
-        <v>110850</v>
+        <v>46984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221049</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Småvänderot</t>
-        </is>
+        <v>102887</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Crunoecia irrorata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Curtis, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granlund, 700 m VSV, Småvänderot, Sk</t>
+          <t>Jula Killa, Degeberga, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443000</v>
+        <v>443031</v>
       </c>
       <c r="R2" t="n">
-        <v>6185899</v>
+        <v>6185958</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -738,19 +742,19 @@
           <t>Degeberga</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>M-Kri-2466</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-07-08</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-07-08</t>
+          <t>2016-04-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Finns från källsprånget (i bladen) och minst 100 m nerströms (under pinnar och enstaka i levermossorna). Mycket fin källa. Måste vara en betydande lokal för arten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,27 +766,349 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kärr i bokskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Martin Stoltze</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Martin Stoltze</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>90326218</v>
+      </c>
+      <c r="B3" t="n">
+        <v>104807</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220464</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lundbräsma</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cardamine impatiens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Granlund, 600 m VSV, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>443061</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6185951</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Degeberga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-06-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-06-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>B9137</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Invid markväg i fuktigare partie</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Lars Fröberg</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Charlotte Wigermo</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122118605</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111128</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Granlund, 700 m VSV, Småvänderot, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>443000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6185899</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Degeberga</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>M-Kri-2466</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2003-07-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2003-07-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kärr i bokskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Ulf Gärdenfors</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>78401233</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Granlund, 600 m VSV, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>443061</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6185951</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Degeberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-06-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-06-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Invid markväg i fuktigare partie</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47662-2025 artfynd.xlsx
+++ b/artfynd/A 47662-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58716499</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90326218</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122118605</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,8 +1129,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78401233</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>